--- a/artfynd/A 47385-2022 artfynd.xlsx
+++ b/artfynd/A 47385-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47385-2022 artfynd.xlsx
+++ b/artfynd/A 47385-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102960072</v>
+        <v>102960024</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503073.1625689304</v>
+        <v>503061</v>
       </c>
       <c r="R2" t="n">
-        <v>7008424.838293467</v>
+        <v>7008431</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102960031</v>
+        <v>102960072</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503060.053178772</v>
+        <v>503074</v>
       </c>
       <c r="R3" t="n">
-        <v>7008431.593971553</v>
+        <v>7008424</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,19 +842,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,37 +871,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102960024</v>
+        <v>102960031</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +907,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503060.053178772</v>
+        <v>503061</v>
       </c>
       <c r="R4" t="n">
-        <v>7008431.593971553</v>
+        <v>7008431</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,19 +940,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,6 +966,421 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>102960207</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Brana Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>503154</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7008449</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-08-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-08-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>102960101</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Brana Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>503132</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7008447</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-08-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-08-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>102960202</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Brana Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>503154</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7008449</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-08-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-08-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>102961850</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Brana Ö , Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>503186</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7008398</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-08-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-08-18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47385-2022 artfynd.xlsx
+++ b/artfynd/A 47385-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102960024</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102960072</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102960031</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102960207</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102960101</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1269,6 +1299,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102960202</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,8 +1416,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102961850</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>